--- a/iFST_online_PsychoPy/ifst_files/instructions.xlsx
+++ b/iFST_online_PsychoPy/ifst_files/instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/ifst_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="14_{D1FB8DA2-A0B5-464E-9B40-0C34DE3DBC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2949CF54-8EC7-4D29-A78F-AA534FA77F51}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{08A17812-2941-4608-8582-45425C42F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F61517FC-D78C-4244-9B2A-E1AF84091710}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,6 +135,24 @@
     <t>left</t>
   </si>
   <si>
+    <t>images/seq_right.png</t>
+  </si>
+  <si>
+    <t>images/seq_left.png</t>
+  </si>
+  <si>
+    <t>images/seq_simple_right.png</t>
+  </si>
+  <si>
+    <t>images/seq_complex_right.png</t>
+  </si>
+  <si>
+    <t>images/seq_execution_right.png</t>
+  </si>
+  <si>
+    <t>images/seq_imagery_right.png</t>
+  </si>
+  <si>
     <t>image_h</t>
   </si>
   <si>
@@ -153,6 +171,9 @@
 Throughout the task, please maintain your hand in this position.</t>
   </si>
   <si>
+    <t>images/seq_simple_left.png</t>
+  </si>
+  <si>
     <t>inst_msg_EN</t>
   </si>
   <si>
@@ -160,6 +181,15 @@
   </si>
   <si>
     <t>inst_pic</t>
+  </si>
+  <si>
+    <t>images/seq_complex_left.png</t>
+  </si>
+  <si>
+    <t>images/seq_execution_left.png</t>
+  </si>
+  <si>
+    <t>images/seq_imagery_left.png</t>
   </si>
   <si>
     <t>In this task you will type or imagine typing two 8-digit sequences with your RIGHT hand. Sometimes you will PHYSICALLY type the sequence. Other times you will only IMAGINE typing the sequence. During imagery, you will be asked to focus on BOTH the: 
@@ -198,15 +228,6 @@
 Tout au long de la tâche, veuillez maintenir votre main dans cette position.</t>
   </si>
   <si>
-    <t>Pour cette tâche, vous utiliserez les quatre doigts de votre main dominante.
-Veuillez placer votre main droite sur le clavier, les doigts sur les touches indiquées :
-J = Index
-H = Majeur
-G = Annulaire
-F = Petit doigt
-Tout au long de la tâche, veuillez maintenir votre main dans cette position.</t>
-  </si>
-  <si>
     <t>Il s'agit d'un exemple de séquence. NE pratiquez PAS la séquence à ce stade.
 Sur l'image, vous pouvez voir que chaque point noir correspond à une pression sur une touche. La ligne noire indique la touche sur laquelle vous devez appuyer ensuite.
 Dans le cas de cette séquence, l'ordre correct serait :
@@ -256,24 +277,6 @@
 Mantén la mano en esta posición durante toda la tarea.</t>
   </si>
   <si>
-    <t>For the task you will use the four fingers of your dominant hand.
-Please place your hand on the keyboard with your fingers on the buttons shown:
-J = Index
-H = Middle
-G = Ring
-F = Little
-Throughout the task, please maintain your hand in this position.</t>
-  </si>
-  <si>
-    <t>Para realizar la tarea, utilizarás los cuatro dedos de tu mano dominante.
-Coloca tu mano sobre el teclado con los dedos sobre las teclas que se indican a continuación:
-J = Índice
-H = Medio
-G = Anular
-F = Meñique
-Mantén la mano en esta posición durante toda la tarea.</t>
-  </si>
-  <si>
     <t>Esta es una secuencia de ejemplo. NO practiques la secuencia en este momento.
 En la imagen, puedes ver que cada punto negro corresponde a una pulsación de tecla. La línea negra indica cuál debería ser la siguiente.
 En el caso de esta secuencia, el orden correcto sería:
@@ -305,36 +308,6 @@
     <t>inst_msg_DE</t>
   </si>
   <si>
-    <t>In dieser Aufgabe werden Sie zwei 8-stellige Sequenzen mit Ihrer RECHTEN Hand tippen oder sich vorstellen zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Zu anderen Zeiten werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
-VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
-KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich Ihre Muskeln zusammenziehen und sich Ihre Gelenke bewegen)
-Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
-  </si>
-  <si>
-    <t>In dieser Aufgabe werden Sie zwei 8-stellige Sequenzen mit Ihrer LINKEN Hand tippen oder sich vorstellen zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Zu anderen Zeiten werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
-VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
-KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich Ihre Muskeln zusammenziehen und sich Ihre Gelenke bewegen)
-Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
-  </si>
-  <si>
-    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
-Bitte legen Sie Ihre RECHTE Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
-F = Zeigefinger
-G = Mittelfinger
-H = Ringfinger
-J = Kleiner Finger
-Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
-  </si>
-  <si>
-    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
-Bitte legen Sie Ihre Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
-J = Zeigefinger
-H = Mittelfinger
-G = Ringfinger
-F = Kleiner Finger
-Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
-  </si>
-  <si>
     <t>Dies ist eine Beispielsequenz. ÜBEN Sie die Sequenz zu diesem Zeitpunkt NICHT.
 Im Bild können Sie sehen, dass jeder schwarze Punkt einem Tastendruck entspricht. Die schwarze Linie zeigt an, welcher Tastendruck als Nächstes erfolgen sollte.
 Im Fall dieser Sequenz wäre die korrekte Reihenfolge:
@@ -358,46 +331,73 @@
 Wenn Sie sich die Bewegungen vorstellen, BEWEGEN Sie Ihre Hand NICHT, halten Sie sie ruhig über den angegebenen Tasten.</t>
   </si>
   <si>
-    <t>Ziel der Aufgabe ist es, die Sequenz sowohl bei der Ausführung als auch bei der Vorstellung so SCHNELL und GENAU wie möglich zu absolvieren.
-Wir bitten Sie jedoch, die GENAUIGKEIT gegenüber der Geschwindigkeit zu PRIORISIEREN. Das heißt, versuchen Sie, die Aufgabe so schnell wie möglich zu erledigen, während Sie sicherstellen, dass Sie die Sequenz korrekt ausführen.
-Sie müssen nicht sofort nach Beginn des Durchgangs mit dem Tippen oder Vorstellen beginnen, aber sobald Sie die Bewegung starten, versuchen Sie, sie so schnell und genau wie möglich abzuschließen.</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_right.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_left.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_simple_right.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_simple_left.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_complex_right.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_complex_left.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_execution_right.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_execution_left.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_imagery_right.png</t>
-  </si>
-  <si>
-    <t>ifst_images/seq_imagery_left.png</t>
+    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
+Bitte legen Sie Ihre rechte Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
+F = Zeigefinger
+G = Mittelfinger
+H = Ringfinger
+J = Kleiner Finger
+Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
+  </si>
+  <si>
+    <t>Ziel der Aufgabe ist es, die Sequenz sowohl bei der Ausführung als auch bei der Vorstellung so SCHNELL und KORREKT wie möglich zu absolvieren.
+Wir bitten Sie jedoch, die KORREKTHEIT gegenüber der Geschwindigkeit zu PRIORISIEREN. Das heißt, versuchen Sie, die Aufgabe so schnell wie möglich zu erledigen, während Sie sicherstellen, dass Sie die Sequenz korrekt ausführen.
+Sie müssen nicht sofort nach Beginn des Durchgangs mit dem Tippen oder Vorstellen beginnen, aber sobald Sie die Bewegung starten, versuchen Sie, sie so schnell und korrekt wie möglich abzuschließen.</t>
+  </si>
+  <si>
+    <t>For the task you will use the four fingers of your dominant hand.
+Please place your left hand on the keyboard with your fingers on the buttons shown:
+J = Index
+H = Middle
+G = Ring
+F = Little
+Throughout the task, please maintain your hand in this position.</t>
+  </si>
+  <si>
+    <t>Para realizar la tarea, utilizarás los cuatro dedos de tu mano dominante.
+Coloca tu mano izquierda sobre el teclado con los dedos sobre las teclas que se indican a continuación:
+J = Índice
+H = Medio
+G = Anular
+F = Meñique
+Mantén la mano en esta posición durante toda la tarea.</t>
+  </si>
+  <si>
+    <t>Pour cette tâche, vous utiliserez les quatre doigts de votre main dominante.
+Veuillez placer votre main gauche sur le clavier, les doigts sur les touches indiquées :
+J = Index
+H = Majeur
+G = Annulaire
+F = Petit doigt
+Tout au long de la tâche, veuillez maintenir votre main dans cette position.</t>
+  </si>
+  <si>
+    <t>Für die Aufgabe verwenden Sie die vier Finger Ihrer dominanten Hand.
+Bitte legen Sie Ihre linke Hand auf die Tastatur, wobei Ihre Finger auf den angezeigten Tasten liegen:
+J = Zeigefinger
+H = Mittelfinger
+G = Ringfinger
+F = Kleiner Finger
+Bitte halten Sie während der gesamten Aufgabe Ihre Hand in dieser Position.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe werden Sie mit Ihrer RECHTEN Hand zwei 8-stellige Sequenzen tippen oder sich vorstellen, diese zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Manchmal werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
+VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
+KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich das Zussammenziehen Ihrer Muskeln und Bewegen Ihrer Gelenke anfühlt)
+Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
+  </si>
+  <si>
+    <t>In dieser Aufgabe werden Sie mit Ihrer LINKEN Hand zwei 8-stellige Sequenzen tippen oder sich vorstellen, diese zu tippen. Manchmal werden Sie die Sequenz PHYSISCH tippen. Manchmal werden Sie sich das Tippen der Sequenz nur VORSTELLEN. Während der Vorstellung werden Sie gebeten, sich auf BEIDE der folgenden Aspekte zu konzentrieren:
+VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
+KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich das Zussammenziehen Ihrer Muskeln und Bewegen Ihrer Gelenke anfühlt)
+Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +434,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -461,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -470,6 +476,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -794,51 +803,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.7265625" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="29.81640625" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="70.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -850,24 +859,24 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -879,24 +888,24 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0.5</v>
@@ -908,24 +917,24 @@
         <v>-0.3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>0.5</v>
@@ -936,25 +945,25 @@
       <c r="E5">
         <v>-0.3</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>41</v>
+      <c r="F5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>0.5</v>
@@ -969,21 +978,21 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>0.5</v>
@@ -998,21 +1007,21 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>0.5</v>
@@ -1027,21 +1036,21 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>0.5</v>
@@ -1056,21 +1065,21 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>0.6</v>
@@ -1085,21 +1094,21 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>0.6</v>
@@ -1114,21 +1123,21 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>0.6</v>
@@ -1143,21 +1152,21 @@
         <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>0.6</v>
@@ -1172,21 +1181,21 @@
         <v>3</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1201,13 +1210,13 @@
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1338,18 +1347,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1369,14 +1378,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1389,4 +1390,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/iFST_online_PsychoPy/ifst_files/instructions.xlsx
+++ b/iFST_online_PsychoPy/ifst_files/instructions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/ifst_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_online_PsychoPy/ifst_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{08A17812-2941-4608-8582-45425C42F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F61517FC-D78C-4244-9B2A-E1AF84091710}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{08A17812-2941-4608-8582-45425C42F179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF748FE-166F-47CF-B061-2E35DB9CAF00}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,24 +135,6 @@
     <t>left</t>
   </si>
   <si>
-    <t>images/seq_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_simple_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_complex_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_execution_right.png</t>
-  </si>
-  <si>
-    <t>images/seq_imagery_right.png</t>
-  </si>
-  <si>
     <t>image_h</t>
   </si>
   <si>
@@ -171,9 +153,6 @@
 Throughout the task, please maintain your hand in this position.</t>
   </si>
   <si>
-    <t>images/seq_simple_left.png</t>
-  </si>
-  <si>
     <t>inst_msg_EN</t>
   </si>
   <si>
@@ -181,15 +160,6 @@
   </si>
   <si>
     <t>inst_pic</t>
-  </si>
-  <si>
-    <t>images/seq_complex_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_execution_left.png</t>
-  </si>
-  <si>
-    <t>images/seq_imagery_left.png</t>
   </si>
   <si>
     <t>In this task you will type or imagine typing two 8-digit sequences with your RIGHT hand. Sometimes you will PHYSICALLY type the sequence. Other times you will only IMAGINE typing the sequence. During imagery, you will be asked to focus on BOTH the: 
@@ -391,6 +361,36 @@
 VISUELLE Aspekte der Bewegung (d. h. sich vorzustellen, wie Sie Ihre Finger aus einer INTERNEN Perspektive bzw. aus der ICH-PERSPEKTIVE bewegen)
 KINÄSTHETISCHE Aspekte der Bewegung (d. h. sich vorzustellen, wie sich das Zussammenziehen Ihrer Muskeln und Bewegen Ihrer Gelenke anfühlt)
 Bitte versuchen Sie immer, sich auf BEIDE ASPEKTE GLEICHZEITIG zu konzentrieren, auch wenn sich dies nicht natürlich anfühlt. Falls Ihnen dies schwergefallen ist, haben Sie nach der Aufgabe die Möglichkeit, Ihre Erfahrung zu erläutern.</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_simple_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_simple_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_complex_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_complex_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_execution_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_execution_left.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_imagery_right.png</t>
+  </si>
+  <si>
+    <t>ifst_images/seq_imagery_left.png</t>
   </si>
 </sst>
 </file>
@@ -475,12 +475,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,405 +814,405 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="I4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="3">
         <v>0.5</v>
       </c>
-      <c r="D4">
+      <c r="D6" s="3">
         <v>0.4</v>
       </c>
-      <c r="E4">
-        <v>-0.3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <v>0.4</v>
-      </c>
-      <c r="E5">
-        <v>-0.3</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <v>0.4</v>
-      </c>
-      <c r="E6">
-        <v>-0.3</v>
+      <c r="E6" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="145" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
         <v>0.5</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>0.4</v>
       </c>
-      <c r="E7">
-        <v>-0.3</v>
+      <c r="E7" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3">
         <v>0.5</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>0.4</v>
       </c>
-      <c r="E8">
-        <v>-0.3</v>
+      <c r="E8" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3">
         <v>0.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>0.4</v>
       </c>
-      <c r="E9">
-        <v>-0.3</v>
+      <c r="E9" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3">
         <v>0.6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>0.5</v>
       </c>
-      <c r="E10">
-        <v>-0.3</v>
+      <c r="E10" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="3">
         <v>0.6</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>0.5</v>
       </c>
-      <c r="E11">
-        <v>-0.3</v>
+      <c r="E11" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3">
         <v>0.6</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>0.5</v>
       </c>
-      <c r="E12">
-        <v>-0.3</v>
+      <c r="E12" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3">
         <v>0.6</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>0.5</v>
       </c>
-      <c r="E13">
-        <v>-0.3</v>
+      <c r="E13" s="3">
+        <v>-0.25</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3">
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1233,6 +1229,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1346,22 +1351,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1377,7 +1381,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1390,12 +1394,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>